--- a/Employee_Reports_wi52/Daniel Bacolcol Orquiza Q0612.xlsx
+++ b/Employee_Reports_wi52/Daniel Bacolcol Orquiza Q0612.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1207,11 +1216,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1271,78 +1280,78 @@
       <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1379,11 +1388,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1392,6 +1401,43 @@
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>728</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1841,7 +1887,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1982,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1965,7 +2011,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1994,7 +2040,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2069,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2052,7 +2098,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2081,7 +2127,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2110,7 +2156,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2185,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2214,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2197,7 +2243,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2272,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2255,7 +2301,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2284,7 +2330,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2359,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2342,7 +2388,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2371,7 +2417,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2400,7 +2446,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2429,7 +2475,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2458,7 +2504,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2487,7 +2533,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2516,7 +2562,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
